--- a/Versuch E7/Daten_E7.xlsx
+++ b/Versuch E7/Daten_E7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fynnlucca/Documents/Grundpraktikum-1/Versuch E7/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B58942-4C68-E94B-BE61-775725A9DE87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F79DC53-1059-3844-BAD4-41D4F1F12A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{FBA0A028-EC3D-6B4A-B90B-9ACFCA4EBE57}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
   <si>
     <t>Kalibrierung</t>
   </si>
@@ -134,6 +134,15 @@
   </si>
   <si>
     <t>Spannung bei dem Versuch runtergegangen: 1.763 V</t>
+  </si>
+  <si>
+    <t>Gruppe 8</t>
+  </si>
+  <si>
+    <t>Fynn Kanja</t>
+  </si>
+  <si>
+    <t>Valentino D'Agosto</t>
   </si>
 </sst>
 </file>
@@ -512,6 +521,15 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
+      <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2" spans="1:61" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
